--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_387CDADADA3AA9B66CFD4D18C5A051F2DB1993B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD127417-EB1F-44FA-86AD-8ABB4806EFE2}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_387CDADADA3AA9B66CFD4D18C5A051F2DB1993B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E470017-5F79-4A53-B753-977DB9F9A4BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -1487,7 +1487,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1569,13 +1569,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -1593,10 +1593,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1642,6 +1642,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1950,15 +1954,21 @@
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="10"/>
+      <c r="L2" s="11">
+        <v>46273</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>233</v>
+      </c>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="11" t="str">
+      <c r="P2" s="11">
         <f>IF(AND($L2&lt;&gt;"",$M2&lt;&gt;""),$L2+VLOOKUP($M2,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q2" s="11"/>
+        <v>46275</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>46278</v>
+      </c>
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
       <c r="T2" s="10" t="s">
@@ -2039,7 +2049,9 @@
         <f>IF(AND($L4&lt;&gt;"",$M4&lt;&gt;""),$L4+VLOOKUP($M4,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46278</v>
       </c>
-      <c r="Q4" s="11"/>
+      <c r="Q4" s="11">
+        <v>46278</v>
+      </c>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
       <c r="T4" s="10" t="s">
@@ -2115,13 +2127,17 @@
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="10"/>
+      <c r="L6" s="11">
+        <v>46278</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>236</v>
+      </c>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
-      <c r="P6" s="11" t="str">
+      <c r="P6" s="11">
         <f>IF(AND($L6&lt;&gt;"",$M6&lt;&gt;""),$L6+VLOOKUP($M6,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46280</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="10"/>
@@ -3636,7 +3652,7 @@
       </c>
       <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">

--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_387CDADADA3AA9B66CFD4D18C5A051F2DB1993B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E470017-5F79-4A53-B753-977DB9F9A4BF}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_387CDADADA3AA9B66CFD4D18C5A051F2DB1993B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{912218EE-3BC4-4846-85B8-40082DF7C3B9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -2170,13 +2170,17 @@
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="6"/>
+      <c r="L7" s="12">
+        <v>46279</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>233</v>
+      </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="12" t="str">
+      <c r="P7" s="12">
         <f>IF(AND($L7&lt;&gt;"",$M7&lt;&gt;""),$L7+VLOOKUP($M7,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46281</v>
       </c>
       <c r="Q7" s="12"/>
       <c r="R7" s="6"/>
@@ -2209,13 +2213,17 @@
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="10"/>
+      <c r="L8" s="11">
+        <v>46279</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>233</v>
+      </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
-      <c r="P8" s="11" t="str">
+      <c r="P8" s="11">
         <f>IF(AND($L8&lt;&gt;"",$M8&lt;&gt;""),$L8+VLOOKUP($M8,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46281</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="10"/>
@@ -3652,7 +3660,7 @@
       </c>
       <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -3671,7 +3679,7 @@
       </c>
       <c r="B8" s="8">
         <f ca="1">COUNTIFS('Master Schedule'!P2:P43,"&lt;="&amp;TODAY(),'Master Schedule'!P2:P43,"&gt;0",'Master Schedule'!Q2:Q43,"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">

--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_0EA98B02D5D38FBAA81C65D3315416646CD29F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB51EAE-0243-4D72-89A1-395F2A947288}"/>
   <bookViews>
-    <workbookView windowWidth="19335" windowHeight="7665"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,25 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Section Plan" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -1466,15 +1485,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1495,158 +1510,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1671,194 +1545,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1866,362 +1554,75 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2235,6 +1636,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2429,14 +1833,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -2458,1708 +1862,1729 @@
     <col min="20" max="20" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:20">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:20" ht="27">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" ht="57" spans="1:20">
-      <c r="A2" s="14">
+    <row r="2" spans="1:20" ht="54">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="11">
         <v>46273</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15">
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11">
         <v>46273</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="15">
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="11">
         <f>IF(AND($L2&lt;&gt;"",$M2&lt;&gt;""),$L2+VLOOKUP($M2,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46275</v>
       </c>
-      <c r="Q2" s="15">
+      <c r="Q2" s="11">
         <v>46278</v>
       </c>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14" t="s">
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="71.25" spans="1:20">
-      <c r="A3" s="10">
+    <row r="3" spans="1:20" ht="67.5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="12">
         <v>46274</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-    </row>
-    <row r="4" ht="42.75" spans="1:20">
-      <c r="A4" s="14">
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:20" ht="40.5">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>46275</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15">
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11">
         <v>46276</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="15">
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11">
         <f>IF(AND($L4&lt;&gt;"",$M4&lt;&gt;""),$L4+VLOOKUP($M4,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46278</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="11">
         <v>46278</v>
       </c>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14" t="s">
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="1:20">
-      <c r="A5" s="10">
+    <row r="5" spans="1:20" ht="40.5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="12">
         <v>46276</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16">
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12">
         <v>46277</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="16">
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="12">
         <f>IF(AND($L5&lt;&gt;"",$M5&lt;&gt;""),$L5+VLOOKUP($M5,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46279</v>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-    </row>
-    <row r="6" ht="28.5" spans="1:20">
-      <c r="A6" s="14">
+      <c r="Q5" s="12">
+        <v>46289</v>
+      </c>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:20" ht="40.5">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>46277</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15">
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11">
         <v>46278</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="15">
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="11">
         <f>IF(AND($L6&lt;&gt;"",$M6&lt;&gt;""),$L6+VLOOKUP($M6,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46280</v>
       </c>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-    </row>
-    <row r="7" ht="28.5" spans="1:20">
-      <c r="A7" s="10">
+      <c r="Q6" s="11">
+        <v>46289</v>
+      </c>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+    </row>
+    <row r="7" spans="1:20" ht="27">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="12">
         <v>46278</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16">
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12">
         <v>46279</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="16">
+      <c r="M7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="12">
         <f>IF(AND($L7&lt;&gt;"",$M7&lt;&gt;""),$L7+VLOOKUP($M7,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46281</v>
       </c>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-    </row>
-    <row r="8" ht="28.5" spans="1:20">
-      <c r="A8" s="14">
+      <c r="Q7" s="12">
+        <v>46289</v>
+      </c>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+    </row>
+    <row r="8" spans="1:20" ht="27">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>46279</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15">
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11">
         <v>46279</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="15">
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="11">
         <f>IF(AND($L8&lt;&gt;"",$M8&lt;&gt;""),$L8+VLOOKUP($M8,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v>46281</v>
       </c>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-    </row>
-    <row r="9" ht="28.5" spans="1:20">
-      <c r="A9" s="10">
+      <c r="Q8" s="11"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+    </row>
+    <row r="9" spans="1:20" ht="40.5">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="12">
         <v>46280</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="16" t="str">
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12">
+        <v>46280</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="12">
         <f>IF(AND($L9&lt;&gt;"",$M9&lt;&gt;""),$L9+VLOOKUP($M9,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-    </row>
-    <row r="10" ht="57" spans="1:20">
-      <c r="A10" s="14">
+        <v>46282</v>
+      </c>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+    </row>
+    <row r="10" spans="1:20" ht="67.5">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>46281</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="11">
         <v>46274</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-    </row>
-    <row r="11" ht="28.5" spans="1:20">
-      <c r="A11" s="10">
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+    </row>
+    <row r="11" spans="1:20" ht="40.5">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="12">
         <v>46282</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16">
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12">
         <v>46282</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="16" t="str">
+      <c r="M11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="12">
         <f>IF(AND($L11&lt;&gt;"",$M11&lt;&gt;""),$L11+VLOOKUP($M11,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:20">
-      <c r="A12" s="14">
+        <v>46284</v>
+      </c>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+    </row>
+    <row r="12" spans="1:20" ht="27">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="11">
         <v>46283</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15">
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11">
         <v>46285</v>
       </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="15" t="str">
+      <c r="M12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="11">
         <f>IF(AND($L12&lt;&gt;"",$M12&lt;&gt;""),$L12+VLOOKUP($M12,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-    </row>
-    <row r="13" ht="42.75" spans="1:20">
-      <c r="A13" s="10">
+        <v>46287</v>
+      </c>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+    </row>
+    <row r="13" spans="1:20" ht="54">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="12">
         <v>46284</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-    </row>
-    <row r="14" ht="57" spans="1:20">
-      <c r="A14" s="14">
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+    </row>
+    <row r="14" spans="1:20" ht="67.5">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="11">
         <v>46285</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14" t="s">
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-    </row>
-    <row r="15" ht="42.75" spans="1:20">
-      <c r="A15" s="10">
+      <c r="I14" s="10"/>
+      <c r="J14" s="11">
+        <v>46287</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+    </row>
+    <row r="15" spans="1:20" ht="54">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="12">
         <v>46286</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="16" t="str">
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12">
+        <v>46290</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="12">
         <f>IF(AND($L15&lt;&gt;"",$M15&lt;&gt;""),$L15+VLOOKUP($M15,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-    </row>
-    <row r="16" ht="42.75" spans="1:20">
-      <c r="A16" s="14">
+        <v>46292</v>
+      </c>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+    </row>
+    <row r="16" spans="1:20" ht="54">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="11">
         <v>46287</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14" t="s">
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="10">
+      <c r="I16" s="10"/>
+      <c r="J16" s="11">
+        <v>46289</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+    </row>
+    <row r="17" spans="1:20" ht="27">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="12">
         <v>46288</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="16" t="str">
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="12" t="str">
         <f>IF(AND($L17&lt;&gt;"",$M17&lt;&gt;""),$L17+VLOOKUP($M17,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-    </row>
-    <row r="18" ht="28.5" spans="1:20">
-      <c r="A18" s="14">
+      <c r="Q17" s="12"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+    </row>
+    <row r="18" spans="1:20" ht="27">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="11">
         <v>46289</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14" t="s">
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="15" t="str">
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="11" t="str">
         <f>IF(AND($L18&lt;&gt;"",$M18&lt;&gt;""),$L18+VLOOKUP($M18,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-    </row>
-    <row r="19" ht="57" spans="1:20">
-      <c r="A19" s="10">
+      <c r="Q18" s="11"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+    </row>
+    <row r="19" spans="1:20" ht="67.5">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="12">
         <v>46290</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10" t="s">
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-    </row>
-    <row r="20" ht="28.5" spans="1:20">
-      <c r="A20" s="14">
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+    </row>
+    <row r="20" spans="1:20" ht="40.5">
+      <c r="A20" s="10">
         <v>19</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="11">
         <v>46291</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="15" t="str">
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="11" t="str">
         <f>IF(AND($L20&lt;&gt;"",$M20&lt;&gt;""),$L20+VLOOKUP($M20,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-    </row>
-    <row r="21" ht="42.75" spans="1:20">
-      <c r="A21" s="10">
+      <c r="Q20" s="11"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+    </row>
+    <row r="21" spans="1:20" ht="40.5">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="12">
         <v>46292</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="16" t="str">
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="12" t="str">
         <f>IF(AND($L21&lt;&gt;"",$M21&lt;&gt;""),$L21+VLOOKUP($M21,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="14">
+      <c r="A22" s="10">
         <v>21</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="11">
         <v>46293</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="15" t="str">
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="11" t="str">
         <f>IF(AND($L22&lt;&gt;"",$M22&lt;&gt;""),$L22+VLOOKUP($M22,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-    </row>
-    <row r="23" ht="28.5" spans="1:20">
-      <c r="A23" s="10">
+      <c r="Q22" s="11"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+    </row>
+    <row r="23" spans="1:20" ht="40.5">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="12">
         <v>46294</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="16" t="str">
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="12" t="str">
         <f>IF(AND($L23&lt;&gt;"",$M23&lt;&gt;""),$L23+VLOOKUP($M23,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-    </row>
-    <row r="24" ht="42.75" spans="1:20">
-      <c r="A24" s="14">
+      <c r="Q23" s="12"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+    </row>
+    <row r="24" spans="1:20" ht="54">
+      <c r="A24" s="10">
         <v>23</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="11">
         <v>46295</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14" t="s">
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-    </row>
-    <row r="25" ht="28.5" spans="1:20">
-      <c r="A25" s="10">
+      <c r="I24" s="10"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+    </row>
+    <row r="25" spans="1:20" ht="40.5">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="12">
         <v>46296</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="16" t="str">
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="12" t="str">
         <f>IF(AND($L25&lt;&gt;"",$M25&lt;&gt;""),$L25+VLOOKUP($M25,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-    </row>
-    <row r="26" ht="42.75" spans="1:20">
-      <c r="A26" s="14">
+      <c r="Q25" s="12"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+    </row>
+    <row r="26" spans="1:20" ht="40.5">
+      <c r="A26" s="10">
         <v>25</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="11">
         <v>46297</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14" t="s">
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="15" t="str">
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="11" t="str">
         <f>IF(AND($L26&lt;&gt;"",$M26&lt;&gt;""),$L26+VLOOKUP($M26,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-    </row>
-    <row r="27" ht="57" spans="1:20">
-      <c r="A27" s="10">
+      <c r="Q26" s="11"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+    </row>
+    <row r="27" spans="1:20" ht="67.5">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="12">
         <v>46298</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10" t="s">
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-    </row>
-    <row r="28" ht="28.5" spans="1:20">
-      <c r="A28" s="14">
+      <c r="I27" s="6"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+    </row>
+    <row r="28" spans="1:20" ht="40.5">
+      <c r="A28" s="10">
         <v>27</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="11">
         <v>46299</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14" t="s">
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="H28" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="15" t="str">
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="11" t="str">
         <f>IF(AND($L28&lt;&gt;"",$M28&lt;&gt;""),$L28+VLOOKUP($M28,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-    </row>
-    <row r="29" ht="57" spans="1:20">
-      <c r="A29" s="10">
+      <c r="Q28" s="11"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+    </row>
+    <row r="29" spans="1:20" ht="67.5">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="12">
         <v>46300</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10" t="s">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="16" t="str">
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="12" t="str">
         <f>IF(AND($L29&lt;&gt;"",$M29&lt;&gt;""),$L29+VLOOKUP($M29,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
-    </row>
-    <row r="30" ht="42.75" spans="1:20">
-      <c r="A30" s="14">
+      <c r="Q29" s="12"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
+    </row>
+    <row r="30" spans="1:20" ht="54">
+      <c r="A30" s="10">
         <v>29</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="11">
         <v>46301</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14" t="s">
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-    </row>
-    <row r="31" ht="42.75" spans="1:20">
-      <c r="A31" s="10">
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+    </row>
+    <row r="31" spans="1:20" ht="54">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="12">
         <v>46302</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-    </row>
-    <row r="32" ht="57" spans="1:20">
-      <c r="A32" s="14">
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+    </row>
+    <row r="32" spans="1:20" ht="67.5">
+      <c r="A32" s="10">
         <v>31</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="11">
         <v>46303</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14" t="s">
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-    </row>
-    <row r="33" ht="28.5" spans="1:20">
-      <c r="A33" s="10">
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+    </row>
+    <row r="33" spans="1:20" ht="27">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="12">
         <v>46304</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10" t="s">
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="16" t="str">
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="12" t="str">
         <f>IF(AND($L33&lt;&gt;"",$M33&lt;&gt;""),$L33+VLOOKUP($M33,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-    </row>
-    <row r="34" ht="28.5" spans="1:20">
-      <c r="A34" s="14">
+      <c r="Q33" s="12"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+    </row>
+    <row r="34" spans="1:20" ht="40.5">
+      <c r="A34" s="10">
         <v>33</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="11">
         <v>46305</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14" t="s">
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H34" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="15" t="str">
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="11" t="str">
         <f>IF(AND($L34&lt;&gt;"",$M34&lt;&gt;""),$L34+VLOOKUP($M34,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-    </row>
-    <row r="35" ht="71.25" spans="1:20">
-      <c r="A35" s="10">
+      <c r="Q34" s="11"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+    </row>
+    <row r="35" spans="1:20" ht="81">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="12">
         <v>46306</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10" t="s">
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="14">
+      <c r="A36" s="10">
         <v>35</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="11">
         <v>46307</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14" t="s">
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="G36" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="H36" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="I36" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="15" t="str">
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="11" t="str">
         <f>IF(AND($L36&lt;&gt;"",$M36&lt;&gt;""),$L36+VLOOKUP($M36,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" s="10">
+      <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="12">
         <v>46308</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10" t="s">
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="16" t="str">
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="12" t="str">
         <f>IF(AND($L37&lt;&gt;"",$M37&lt;&gt;""),$L37+VLOOKUP($M37,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-    </row>
-    <row r="38" ht="28.5" spans="1:20">
-      <c r="A38" s="14">
+      <c r="Q37" s="12"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+    </row>
+    <row r="38" spans="1:20" ht="27">
+      <c r="A38" s="10">
         <v>37</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="11">
         <v>46309</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14" t="s">
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="15" t="str">
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="11" t="str">
         <f>IF(AND($L38&lt;&gt;"",$M38&lt;&gt;""),$L38+VLOOKUP($M38,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
-    </row>
-    <row r="39" ht="57" spans="1:20">
-      <c r="A39" s="10">
+      <c r="Q38" s="11"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+    </row>
+    <row r="39" spans="1:20" ht="54">
+      <c r="A39" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="12">
         <v>46310</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10" t="s">
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="16" t="str">
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="12" t="str">
         <f>IF(AND($L39&lt;&gt;"",$M39&lt;&gt;""),$L39+VLOOKUP($M39,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-    </row>
-    <row r="40" ht="57" spans="1:20">
-      <c r="A40" s="14">
+      <c r="Q39" s="12"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+    </row>
+    <row r="40" spans="1:20" ht="54">
+      <c r="A40" s="10">
         <v>39</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="11">
         <v>46311</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14" t="s">
+      <c r="D40" s="10"/>
+      <c r="E40" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14" t="s">
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="I40" s="14" t="s">
+      <c r="I40" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-    </row>
-    <row r="41" ht="57" spans="1:20">
-      <c r="A41" s="10">
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+    </row>
+    <row r="41" spans="1:20" ht="67.5">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="12">
         <v>46312</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10" t="s">
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-    </row>
-    <row r="42" ht="42.75" spans="1:20">
-      <c r="A42" s="14">
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+    </row>
+    <row r="42" spans="1:20" ht="54">
+      <c r="A42" s="10">
         <v>41</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="11">
         <v>46313</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14" t="s">
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
-    </row>
-    <row r="43" ht="28.5" spans="1:20">
-      <c r="A43" s="10">
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+    </row>
+    <row r="43" spans="1:20" ht="40.5">
+      <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="12">
         <v>46314</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10" t="s">
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="12"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="P2:P43">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(P2&lt;&gt;"",P2&lt;=TODAY(),Q2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="S2:S43">
-      <formula1>"Yes,No,Not requested"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="M2:M43">
+    <dataValidation type="list" sqref="M2:M43" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Totally ignorance,Spark,Skeleton,Crack it"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:O43">
+    <dataValidation type="list" sqref="O2:O43" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R2:R43">
+    <dataValidation type="list" sqref="R2:R43" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Independent,Still Spark,Still Skeleton,Needs Hint,Parked"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2:S43" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>"Yes,No,Not requested"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4169,316 +3594,316 @@
     <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:6">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" ht="18.75">
+      <c r="A1" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" ht="15" spans="1:6">
-      <c r="A4" s="11" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:6" ht="27">
+      <c r="A5" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="8">
         <f>COUNTIF('Exercise Map'!F4:F39,"Yes")</f>
         <v>26</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="6" ht="28.5" spans="1:6">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" ht="27">
+      <c r="A6" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="8">
         <f>COUNTIF('Exercise Map'!F4:F39,"No")</f>
         <v>10</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:6">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:6" ht="27">
+      <c r="A7" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>8</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:6" ht="27">
+      <c r="A8" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="8">
         <f ca="1">COUNTIFS('Master Schedule'!P2:P43,"&lt;="&amp;TODAY(),'Master Schedule'!P2:P43,"&gt;0",'Master Schedule'!Q2:Q43,"")</f>
         <v>4</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="9" ht="28.5" spans="1:6">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:6" ht="27">
+      <c r="A9" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="8">
         <f>COUNT('Section Plan'!J4:J14)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="6" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" ht="15" spans="1:6">
-      <c r="A12" s="13" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" ht="28.5" spans="1:6">
-      <c r="A13" s="10" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" spans="1:6" ht="27">
+      <c r="A13" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" ht="28.5" spans="1:6">
-      <c r="A14" s="10" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="27">
+      <c r="A14" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" ht="28.5" spans="1:6">
-      <c r="A16" s="10" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="40.5">
+      <c r="A16" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" ht="28.5" spans="1:6">
-      <c r="A18" s="10" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="27">
+      <c r="A18" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" ht="15" spans="1:6">
-      <c r="A20" s="13" t="s">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" ht="28.5" spans="1:6">
-      <c r="A21" s="10" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="1:6" ht="40.5">
+      <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" ht="28.5" spans="1:6">
-      <c r="A22" s="10" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="40.5">
+      <c r="A22" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" ht="28.5" spans="1:6">
-      <c r="A23" s="10" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" ht="27">
+      <c r="A23" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4487,16 +3912,15 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -4504,225 +3928,224 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" ht="27">
+      <c r="A1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="2" ht="28.5" spans="1:4">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" ht="40.5">
+      <c r="A2" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="28.5" spans="1:4">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:4" ht="27">
+      <c r="A3" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:4">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" ht="27">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:4">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" ht="27">
+      <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" ht="15" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="27">
+      <c r="A8" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" ht="42.75" spans="1:4">
-      <c r="A9" s="6" t="s">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="40.5">
+      <c r="A9" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" ht="28.5" spans="1:4">
-      <c r="A10" s="4" t="s">
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="40.5">
+      <c r="A10" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" ht="28.5" spans="1:4">
-      <c r="A11" s="6" t="s">
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="40.5">
+      <c r="A11" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:4">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="40.5">
+      <c r="A12" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" ht="28.5" spans="1:4">
-      <c r="A13" s="6" t="s">
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="27">
+      <c r="A13" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" ht="28.5" spans="1:4">
-      <c r="A14" s="4" t="s">
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="40.5">
+      <c r="A14" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" ht="28.5" spans="1:4">
-      <c r="A15" s="6" t="s">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" ht="40.5">
+      <c r="A15" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" ht="28.5" spans="1:4">
-      <c r="A16" s="4" t="s">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="40.5">
+      <c r="A16" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" ht="28.5" spans="1:4">
-      <c r="A17" s="6" t="s">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="40.5">
+      <c r="A17" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4735,1102 +4158,1102 @@
     <col min="9" max="9" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="18.75">
+      <c r="A1" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" ht="30" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" ht="27">
+      <c r="A3" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:9">
-      <c r="A4" s="4">
+    <row r="4" spans="1:9" ht="27">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="2" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:9">
-      <c r="A5" s="6">
+    <row r="5" spans="1:9" ht="27">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="6" ht="42.75" spans="1:9">
-      <c r="A6" s="4">
+    <row r="6" spans="1:9" ht="40.5">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="2" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:9">
-      <c r="A7" s="6">
+    <row r="7" spans="1:9" ht="40.5">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="8" ht="28.5" spans="1:9">
-      <c r="A8" s="4">
+    <row r="8" spans="1:9" ht="27">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="9" ht="28.5" spans="1:9">
-      <c r="A9" s="6">
+    <row r="9" spans="1:9" ht="27">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="2" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="4" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="6">
+    <row r="13" spans="1:9" ht="27">
+      <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6">
+    <row r="15" spans="1:9" ht="27">
+      <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="4" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="16" ht="28.5" spans="1:9">
-      <c r="A16" s="4">
+    <row r="16" spans="1:9" ht="40.5">
+      <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6">
+    <row r="17" spans="1:9" ht="27">
+      <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="4" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="4">
+    <row r="18" spans="1:9" ht="27">
+      <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="19" ht="28.5" spans="1:9">
-      <c r="A19" s="6">
+    <row r="19" spans="1:9" ht="27">
+      <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="4" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="20" ht="28.5" spans="1:9">
-      <c r="A20" s="4">
+    <row r="20" spans="1:9" ht="27">
+      <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="2" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>18</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="4" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>19</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6">
+    <row r="23" spans="1:9" ht="27">
+      <c r="A23" s="4">
         <v>20</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="4">
+    <row r="24" spans="1:9" ht="27">
+      <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="2" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>22</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="4" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="4">
+    <row r="26" spans="1:9" ht="27">
+      <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="27" ht="28.5" spans="1:9">
-      <c r="A27" s="6">
+    <row r="27" spans="1:9" ht="27">
+      <c r="A27" s="4">
         <v>24</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="4" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="28" ht="28.5" spans="1:9">
-      <c r="A28" s="4">
+    <row r="28" spans="1:9" ht="27">
+      <c r="A28" s="2">
         <v>25</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="2" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="4" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="31" ht="28.5" spans="1:9">
-      <c r="A31" s="6">
+    <row r="31" spans="1:9" ht="27">
+      <c r="A31" s="4">
         <v>28</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="4" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6">
+    <row r="33" spans="1:9" ht="27">
+      <c r="A33" s="4">
         <v>30</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="34" ht="28.5" spans="1:9">
-      <c r="A34" s="4">
+    <row r="34" spans="1:9" ht="27">
+      <c r="A34" s="2">
         <v>31</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="2" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>32</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="4">
+    <row r="36" spans="1:9" ht="27">
+      <c r="A36" s="2">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>34</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H37" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="4" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="38" ht="28.5" spans="1:9">
-      <c r="A38" s="4">
+    <row r="38" spans="1:9" ht="27">
+      <c r="A38" s="2">
         <v>35</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="39" ht="28.5" spans="1:9">
-      <c r="A39" s="6">
+    <row r="39" spans="1:9" ht="27">
+      <c r="A39" s="4">
         <v>36</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="4" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5839,16 +5262,15 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5862,353 +5284,353 @@
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="18.75">
+      <c r="A1" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" spans="1:11" ht="27">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="57" spans="1:11">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:11" ht="67.5">
+      <c r="A4" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="4" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" ht="54">
+      <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="6" t="s">
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:11" ht="54">
+      <c r="A6" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="4" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:11" ht="40.5">
+      <c r="A7" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="4" t="s">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="40.5">
+      <c r="A8" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="6" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="54">
+      <c r="A9" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6" t="s">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="10" ht="42.75" spans="1:11">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:11" ht="54">
+      <c r="A10" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" ht="42.75" spans="1:11">
-      <c r="A11" s="6" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="40.5">
+      <c r="A11" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="4" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="40.5">
+      <c r="A12" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="4" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="2" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="13" ht="28.5" spans="1:11">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:11" ht="40.5">
+      <c r="A13" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" ht="42.75" spans="1:11">
-      <c r="A14" s="4" t="s">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="40.5">
+      <c r="A14" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="4" t="s">
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="2" t="s">
         <v>480</v>
       </c>
     </row>
@@ -6217,7 +5639,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0EA98B02D5D38FBAA81C65D3315416646CD29F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB51EAE-0243-4D72-89A1-395F2A947288}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_0EA98B02D5D38FBAA81C65D3315416646CD29F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A6B4A0B-98E0-4D46-ADF3-B0CF224AB93B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -1642,6 +1642,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1840,7 +1844,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1862,7 +1866,7 @@
     <col min="20" max="20" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="27">
+    <row r="1" spans="1:20" ht="28">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1924,7 +1928,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="54">
+    <row r="2" spans="1:20" ht="56">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -1971,7 +1975,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="67.5">
+    <row r="3" spans="1:20" ht="70">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -2007,7 +2011,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" ht="40.5">
+    <row r="4" spans="1:20" ht="42">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -2054,7 +2058,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="40.5">
+    <row r="5" spans="1:20" ht="42">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -2099,7 +2103,7 @@
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:20" ht="40.5">
+    <row r="6" spans="1:20" ht="42">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -2144,7 +2148,7 @@
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
     </row>
-    <row r="7" spans="1:20" ht="27">
+    <row r="7" spans="1:20" ht="28">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -2189,7 +2193,7 @@
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:20" ht="27">
+    <row r="8" spans="1:20" ht="28">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -2232,7 +2236,7 @@
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
     </row>
-    <row r="9" spans="1:20" ht="40.5">
+    <row r="9" spans="1:20" ht="42">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -2275,7 +2279,7 @@
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:20" ht="67.5">
+    <row r="10" spans="1:20" ht="70">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -2313,7 +2317,7 @@
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
     </row>
-    <row r="11" spans="1:20" ht="40.5">
+    <row r="11" spans="1:20" ht="42">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -2356,7 +2360,7 @@
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:20" ht="27">
+    <row r="12" spans="1:20" ht="28">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -2399,7 +2403,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
     </row>
-    <row r="13" spans="1:20" ht="54">
+    <row r="13" spans="1:20" ht="56">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -2435,7 +2439,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:20" ht="67.5">
+    <row r="14" spans="1:20" ht="70">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -2471,7 +2475,7 @@
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
     </row>
-    <row r="15" spans="1:20" ht="54">
+    <row r="15" spans="1:20" ht="56">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -2514,7 +2518,7 @@
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:20" ht="54">
+    <row r="16" spans="1:20" ht="56">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -2550,7 +2554,7 @@
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
     </row>
-    <row r="17" spans="1:20" ht="27">
+    <row r="17" spans="1:20" ht="28">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -2576,20 +2580,24 @@
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="6"/>
+      <c r="L17" s="12">
+        <v>46292</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
-      <c r="P17" s="12" t="str">
+      <c r="P17" s="12">
         <f>IF(AND($L17&lt;&gt;"",$M17&lt;&gt;""),$L17+VLOOKUP($M17,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46294</v>
       </c>
       <c r="Q17" s="12"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="1:20" ht="27">
+    <row r="18" spans="1:20" ht="28">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -2628,7 +2636,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20" ht="67.5">
+    <row r="19" spans="1:20" ht="70">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -2664,7 +2672,7 @@
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
     </row>
-    <row r="20" spans="1:20" ht="40.5">
+    <row r="20" spans="1:20" ht="42">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -2703,7 +2711,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
     </row>
-    <row r="21" spans="1:20" ht="40.5">
+    <row r="21" spans="1:20" ht="42">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -2781,7 +2789,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
     </row>
-    <row r="23" spans="1:20" ht="40.5">
+    <row r="23" spans="1:20" ht="42">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -2820,7 +2828,7 @@
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
     </row>
-    <row r="24" spans="1:20" ht="54">
+    <row r="24" spans="1:20" ht="56">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -2854,7 +2862,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
     </row>
-    <row r="25" spans="1:20" ht="40.5">
+    <row r="25" spans="1:20" ht="42">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -2893,7 +2901,7 @@
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
     </row>
-    <row r="26" spans="1:20" ht="40.5">
+    <row r="26" spans="1:20" ht="42">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -2932,7 +2940,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
     </row>
-    <row r="27" spans="1:20" ht="67.5">
+    <row r="27" spans="1:20" ht="70">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -2966,7 +2974,7 @@
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
     </row>
-    <row r="28" spans="1:20" ht="40.5">
+    <row r="28" spans="1:20" ht="42">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -3005,7 +3013,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
     </row>
-    <row r="29" spans="1:20" ht="67.5">
+    <row r="29" spans="1:20" ht="70">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -3044,7 +3052,7 @@
       <c r="S29" s="6"/>
       <c r="T29" s="6"/>
     </row>
-    <row r="30" spans="1:20" ht="54">
+    <row r="30" spans="1:20" ht="56">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -3080,7 +3088,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
     </row>
-    <row r="31" spans="1:20" ht="54">
+    <row r="31" spans="1:20" ht="56">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -3114,7 +3122,7 @@
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
     </row>
-    <row r="32" spans="1:20" ht="67.5">
+    <row r="32" spans="1:20" ht="70">
       <c r="A32" s="10">
         <v>31</v>
       </c>
@@ -3150,7 +3158,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
     </row>
-    <row r="33" spans="1:20" ht="27">
+    <row r="33" spans="1:20" ht="28">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -3189,7 +3197,7 @@
       <c r="S33" s="6"/>
       <c r="T33" s="6"/>
     </row>
-    <row r="34" spans="1:20" ht="40.5">
+    <row r="34" spans="1:20" ht="42">
       <c r="A34" s="10">
         <v>33</v>
       </c>
@@ -3228,7 +3236,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
     </row>
-    <row r="35" spans="1:20" ht="81">
+    <row r="35" spans="1:20" ht="84">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -3340,7 +3348,7 @@
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" spans="1:20" ht="27">
+    <row r="38" spans="1:20" ht="28">
       <c r="A38" s="10">
         <v>37</v>
       </c>
@@ -3379,7 +3387,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
     </row>
-    <row r="39" spans="1:20" ht="54">
+    <row r="39" spans="1:20" ht="56">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -3418,7 +3426,7 @@
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" spans="1:20" ht="54">
+    <row r="40" spans="1:20" ht="56">
       <c r="A40" s="10">
         <v>39</v>
       </c>
@@ -3452,7 +3460,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
     </row>
-    <row r="41" spans="1:20" ht="67.5">
+    <row r="41" spans="1:20" ht="70">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -3488,7 +3496,7 @@
       <c r="S41" s="6"/>
       <c r="T41" s="6"/>
     </row>
-    <row r="42" spans="1:20" ht="54">
+    <row r="42" spans="1:20" ht="56">
       <c r="A42" s="10">
         <v>41</v>
       </c>
@@ -3522,7 +3530,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
     </row>
-    <row r="43" spans="1:20" ht="40.5">
+    <row r="43" spans="1:20" ht="42">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -3584,7 +3592,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -3594,7 +3602,7 @@
     <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75">
+    <row r="1" spans="1:6" ht="17.5">
       <c r="A1" s="13" t="s">
         <v>176</v>
       </c>
@@ -3640,7 +3648,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="27">
+    <row r="5" spans="1:6" ht="28">
       <c r="A5" s="6" t="s">
         <v>183</v>
       </c>
@@ -3659,7 +3667,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="27">
+    <row r="6" spans="1:6" ht="28">
       <c r="A6" s="6" t="s">
         <v>186</v>
       </c>
@@ -3678,13 +3686,13 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="27">
+    <row r="7" spans="1:6" ht="28">
       <c r="A7" s="6" t="s">
         <v>190</v>
       </c>
       <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -3697,13 +3705,13 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="27">
+    <row r="8" spans="1:6" ht="28">
       <c r="A8" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B8" s="8">
         <f ca="1">COUNTIFS('Master Schedule'!P2:P43,"&lt;="&amp;TODAY(),'Master Schedule'!P2:P43,"&gt;0",'Master Schedule'!Q2:Q43,"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
@@ -3716,7 +3724,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="27">
+    <row r="9" spans="1:6" ht="28">
       <c r="A9" s="6" t="s">
         <v>196</v>
       </c>
@@ -3761,7 +3769,7 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:6" ht="27">
+    <row r="13" spans="1:6" ht="28">
       <c r="A13" s="6" t="s">
         <v>200</v>
       </c>
@@ -3775,7 +3783,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="27">
+    <row r="14" spans="1:6" ht="28">
       <c r="A14" s="6" t="s">
         <v>203</v>
       </c>
@@ -3803,7 +3811,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="40.5">
+    <row r="16" spans="1:6" ht="42">
       <c r="A16" s="6" t="s">
         <v>209</v>
       </c>
@@ -3831,7 +3839,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="27">
+    <row r="18" spans="1:6" ht="28">
       <c r="A18" s="6" t="s">
         <v>215</v>
       </c>
@@ -3863,7 +3871,7 @@
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6" ht="40.5">
+    <row r="21" spans="1:6" ht="42">
       <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
@@ -3877,7 +3885,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="40.5">
+    <row r="22" spans="1:6" ht="42">
       <c r="A22" s="6" t="s">
         <v>121</v>
       </c>
@@ -3891,7 +3899,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="27">
+    <row r="23" spans="1:6" ht="28">
       <c r="A23" s="6" t="s">
         <v>155</v>
       </c>
@@ -3920,7 +3928,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3928,7 +3936,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27">
+    <row r="1" spans="1:4" ht="28">
       <c r="A1" s="1" t="s">
         <v>225</v>
       </c>
@@ -3942,7 +3950,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="40.5">
+    <row r="2" spans="1:4" ht="42">
       <c r="A2" s="2" t="s">
         <v>229</v>
       </c>
@@ -3956,7 +3964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="27">
+    <row r="3" spans="1:4" ht="28">
       <c r="A3" s="4" t="s">
         <v>232</v>
       </c>
@@ -3970,7 +3978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27">
+    <row r="4" spans="1:4" ht="28">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -3984,7 +3992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27">
+    <row r="5" spans="1:4" ht="28">
       <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
@@ -4016,7 +4024,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="27">
+    <row r="8" spans="1:4" ht="28">
       <c r="A8" s="2" t="s">
         <v>241</v>
       </c>
@@ -4028,7 +4036,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="40.5">
+    <row r="9" spans="1:4" ht="42">
       <c r="A9" s="4" t="s">
         <v>244</v>
       </c>
@@ -4040,7 +4048,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="40.5">
+    <row r="10" spans="1:4" ht="42">
       <c r="A10" s="2" t="s">
         <v>247</v>
       </c>
@@ -4052,7 +4060,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" ht="40.5">
+    <row r="11" spans="1:4" ht="42">
       <c r="A11" s="4" t="s">
         <v>250</v>
       </c>
@@ -4064,7 +4072,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="40.5">
+    <row r="12" spans="1:4" ht="42">
       <c r="A12" s="2" t="s">
         <v>253</v>
       </c>
@@ -4076,7 +4084,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="27">
+    <row r="13" spans="1:4" ht="28">
       <c r="A13" s="4" t="s">
         <v>256</v>
       </c>
@@ -4088,7 +4096,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="40.5">
+    <row r="14" spans="1:4" ht="42">
       <c r="A14" s="2" t="s">
         <v>259</v>
       </c>
@@ -4100,7 +4108,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="40.5">
+    <row r="15" spans="1:4" ht="42">
       <c r="A15" s="4" t="s">
         <v>262</v>
       </c>
@@ -4112,7 +4120,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="40.5">
+    <row r="16" spans="1:4" ht="42">
       <c r="A16" s="2" t="s">
         <v>265</v>
       </c>
@@ -4124,7 +4132,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="40.5">
+    <row r="17" spans="1:4" ht="42">
       <c r="A17" s="4" t="s">
         <v>268</v>
       </c>
@@ -4145,7 +4153,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4158,7 +4166,7 @@
     <col min="9" max="9" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75">
+    <row r="1" spans="1:9" ht="17.5">
       <c r="A1" s="16" t="s">
         <v>271</v>
       </c>
@@ -4184,7 +4192,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" ht="27">
+    <row r="3" spans="1:9" ht="28">
       <c r="A3" s="1" t="s">
         <v>273</v>
       </c>
@@ -4213,7 +4221,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="27">
+    <row r="4" spans="1:9" ht="28">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -4242,7 +4250,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27">
+    <row r="5" spans="1:9" ht="28">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -4271,7 +4279,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="40.5">
+    <row r="6" spans="1:9" ht="42">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -4300,7 +4308,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="40.5">
+    <row r="7" spans="1:9" ht="42">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -4329,7 +4337,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27">
+    <row r="8" spans="1:9" ht="28">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -4358,7 +4366,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="27">
+    <row r="9" spans="1:9" ht="28">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -4474,7 +4482,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="27">
+    <row r="13" spans="1:9" ht="28">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -4532,7 +4540,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="27">
+    <row r="15" spans="1:9" ht="28">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -4561,7 +4569,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="40.5">
+    <row r="16" spans="1:9" ht="42">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -4590,7 +4598,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="27">
+    <row r="17" spans="1:9" ht="28">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -4619,7 +4627,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="27">
+    <row r="18" spans="1:9" ht="28">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -4648,7 +4656,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="27">
+    <row r="19" spans="1:9" ht="28">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -4677,7 +4685,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="27">
+    <row r="20" spans="1:9" ht="28">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -4764,7 +4772,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27">
+    <row r="23" spans="1:9" ht="28">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -4793,7 +4801,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="27">
+    <row r="24" spans="1:9" ht="28">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -4851,7 +4859,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="27">
+    <row r="26" spans="1:9" ht="28">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -4880,7 +4888,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="27">
+    <row r="27" spans="1:9" ht="28">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -4909,7 +4917,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="27">
+    <row r="28" spans="1:9" ht="28">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -4996,7 +5004,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="27">
+    <row r="31" spans="1:9" ht="28">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -5054,7 +5062,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27">
+    <row r="33" spans="1:9" ht="28">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -5083,7 +5091,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27">
+    <row r="34" spans="1:9" ht="28">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -5141,7 +5149,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="27">
+    <row r="36" spans="1:9" ht="28">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -5199,7 +5207,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27">
+    <row r="38" spans="1:9" ht="28">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -5228,7 +5236,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="27">
+    <row r="39" spans="1:9" ht="28">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -5270,7 +5278,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5284,7 +5292,7 @@
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75">
+    <row r="1" spans="1:11" ht="17.5">
       <c r="A1" s="16" t="s">
         <v>404</v>
       </c>
@@ -5314,7 +5322,7 @@
       <c r="J2" s="17"/>
       <c r="K2" s="17"/>
     </row>
-    <row r="3" spans="1:11" ht="27">
+    <row r="3" spans="1:11" ht="28">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5349,7 +5357,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="67.5">
+    <row r="4" spans="1:11" ht="70">
       <c r="A4" s="2" t="s">
         <v>415</v>
       </c>
@@ -5378,7 +5386,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="54">
+    <row r="5" spans="1:11" ht="56">
       <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
@@ -5405,7 +5413,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="54">
+    <row r="6" spans="1:11" ht="56">
       <c r="A6" s="2" t="s">
         <v>429</v>
       </c>
@@ -5430,7 +5438,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="40.5">
+    <row r="7" spans="1:11" ht="42">
       <c r="A7" s="4" t="s">
         <v>435</v>
       </c>
@@ -5453,7 +5461,7 @@
       <c r="J7" s="5"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="40.5">
+    <row r="8" spans="1:11" ht="42">
       <c r="A8" s="2" t="s">
         <v>439</v>
       </c>
@@ -5480,7 +5488,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="54">
+    <row r="9" spans="1:11" ht="56">
       <c r="A9" s="4" t="s">
         <v>98</v>
       </c>
@@ -5507,7 +5515,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="54">
+    <row r="10" spans="1:11" ht="56">
       <c r="A10" s="2" t="s">
         <v>452</v>
       </c>
@@ -5530,7 +5538,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="40.5">
+    <row r="11" spans="1:11" ht="42">
       <c r="A11" s="4" t="s">
         <v>457</v>
       </c>
@@ -5557,7 +5565,7 @@
       <c r="J11" s="5"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="40.5">
+    <row r="12" spans="1:11" ht="42">
       <c r="A12" s="2" t="s">
         <v>463</v>
       </c>
@@ -5582,7 +5590,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="40.5">
+    <row r="13" spans="1:11" ht="42">
       <c r="A13" s="4" t="s">
         <v>142</v>
       </c>
@@ -5607,7 +5615,7 @@
       <c r="J13" s="5"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="40.5">
+    <row r="14" spans="1:11" ht="42">
       <c r="A14" s="2" t="s">
         <v>474</v>
       </c>

--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_0EA98B02D5D38FBAA81C65D3315416646CD29F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A6B4A0B-98E0-4D46-ADF3-B0CF224AB93B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_DE2EFB3A9D1E79C6859C80A3377C0E0772D29E3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF23E7C9-3F0B-47DB-9547-EF99EC340627}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -1642,10 +1642,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1844,7 +1840,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1866,7 +1862,7 @@
     <col min="20" max="20" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="28">
+    <row r="1" spans="1:20" ht="27">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1928,7 +1924,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="56">
+    <row r="2" spans="1:20" ht="54">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -1975,7 +1971,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="70">
+    <row r="3" spans="1:20" ht="67.5">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -2011,7 +2007,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" ht="42">
+    <row r="4" spans="1:20" ht="40.5">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -2058,7 +2054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="42">
+    <row r="5" spans="1:20" ht="40.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -2103,7 +2099,7 @@
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:20" ht="42">
+    <row r="6" spans="1:20" ht="40.5">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -2148,7 +2144,7 @@
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
     </row>
-    <row r="7" spans="1:20" ht="28">
+    <row r="7" spans="1:20" ht="27">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -2193,7 +2189,7 @@
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:20" ht="28">
+    <row r="8" spans="1:20" ht="27">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -2236,7 +2232,7 @@
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
     </row>
-    <row r="9" spans="1:20" ht="42">
+    <row r="9" spans="1:20" ht="40.5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -2279,7 +2275,7 @@
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:20" ht="70">
+    <row r="10" spans="1:20" ht="67.5">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -2317,7 +2313,7 @@
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
     </row>
-    <row r="11" spans="1:20" ht="42">
+    <row r="11" spans="1:20" ht="40.5">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -2360,7 +2356,7 @@
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:20" ht="28">
+    <row r="12" spans="1:20" ht="27">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -2403,7 +2399,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
     </row>
-    <row r="13" spans="1:20" ht="56">
+    <row r="13" spans="1:20" ht="54">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -2439,7 +2435,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:20" ht="70">
+    <row r="14" spans="1:20" ht="67.5">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -2475,7 +2471,7 @@
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
     </row>
-    <row r="15" spans="1:20" ht="56">
+    <row r="15" spans="1:20" ht="54">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -2518,7 +2514,7 @@
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:20" ht="56">
+    <row r="16" spans="1:20" ht="54">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -2554,7 +2550,7 @@
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
     </row>
-    <row r="17" spans="1:20" ht="28">
+    <row r="17" spans="1:20" ht="27">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -2597,7 +2593,7 @@
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="1:20" ht="28">
+    <row r="18" spans="1:20" ht="27">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -2623,20 +2619,24 @@
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="10"/>
+      <c r="L18" s="11">
+        <v>46292</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
-      <c r="P18" s="11" t="str">
+      <c r="P18" s="11">
         <f>IF(AND($L18&lt;&gt;"",$M18&lt;&gt;""),$L18+VLOOKUP($M18,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46294</v>
       </c>
       <c r="Q18" s="11"/>
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20" ht="70">
+    <row r="19" spans="1:20" ht="67.5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -2672,7 +2672,7 @@
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
     </row>
-    <row r="20" spans="1:20" ht="42">
+    <row r="20" spans="1:20" ht="40.5">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -2698,20 +2698,24 @@
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="10"/>
+      <c r="L20" s="11">
+        <v>46299</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
-      <c r="P20" s="11" t="str">
+      <c r="P20" s="11">
         <f>IF(AND($L20&lt;&gt;"",$M20&lt;&gt;""),$L20+VLOOKUP($M20,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46301</v>
       </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="10"/>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
     </row>
-    <row r="21" spans="1:20" ht="42">
+    <row r="21" spans="1:20" ht="40.5">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -2789,7 +2793,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
     </row>
-    <row r="23" spans="1:20" ht="42">
+    <row r="23" spans="1:20" ht="40.5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -2828,7 +2832,7 @@
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
     </row>
-    <row r="24" spans="1:20" ht="56">
+    <row r="24" spans="1:20" ht="54">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -2862,7 +2866,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
     </row>
-    <row r="25" spans="1:20" ht="42">
+    <row r="25" spans="1:20" ht="40.5">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -2901,7 +2905,7 @@
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
     </row>
-    <row r="26" spans="1:20" ht="42">
+    <row r="26" spans="1:20" ht="40.5">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -2940,7 +2944,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
     </row>
-    <row r="27" spans="1:20" ht="70">
+    <row r="27" spans="1:20" ht="67.5">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -2974,7 +2978,7 @@
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
     </row>
-    <row r="28" spans="1:20" ht="42">
+    <row r="28" spans="1:20" ht="40.5">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -3013,7 +3017,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
     </row>
-    <row r="29" spans="1:20" ht="70">
+    <row r="29" spans="1:20" ht="67.5">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -3052,7 +3056,7 @@
       <c r="S29" s="6"/>
       <c r="T29" s="6"/>
     </row>
-    <row r="30" spans="1:20" ht="56">
+    <row r="30" spans="1:20" ht="54">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -3088,7 +3092,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
     </row>
-    <row r="31" spans="1:20" ht="56">
+    <row r="31" spans="1:20" ht="54">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -3122,7 +3126,7 @@
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
     </row>
-    <row r="32" spans="1:20" ht="70">
+    <row r="32" spans="1:20" ht="67.5">
       <c r="A32" s="10">
         <v>31</v>
       </c>
@@ -3158,7 +3162,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
     </row>
-    <row r="33" spans="1:20" ht="28">
+    <row r="33" spans="1:20" ht="27">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -3197,7 +3201,7 @@
       <c r="S33" s="6"/>
       <c r="T33" s="6"/>
     </row>
-    <row r="34" spans="1:20" ht="42">
+    <row r="34" spans="1:20" ht="40.5">
       <c r="A34" s="10">
         <v>33</v>
       </c>
@@ -3236,7 +3240,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
     </row>
-    <row r="35" spans="1:20" ht="84">
+    <row r="35" spans="1:20" ht="81">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -3348,7 +3352,7 @@
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" spans="1:20" ht="28">
+    <row r="38" spans="1:20" ht="27">
       <c r="A38" s="10">
         <v>37</v>
       </c>
@@ -3387,7 +3391,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
     </row>
-    <row r="39" spans="1:20" ht="56">
+    <row r="39" spans="1:20" ht="54">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -3426,7 +3430,7 @@
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" spans="1:20" ht="56">
+    <row r="40" spans="1:20" ht="54">
       <c r="A40" s="10">
         <v>39</v>
       </c>
@@ -3460,7 +3464,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
     </row>
-    <row r="41" spans="1:20" ht="70">
+    <row r="41" spans="1:20" ht="67.5">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -3496,7 +3500,7 @@
       <c r="S41" s="6"/>
       <c r="T41" s="6"/>
     </row>
-    <row r="42" spans="1:20" ht="56">
+    <row r="42" spans="1:20" ht="54">
       <c r="A42" s="10">
         <v>41</v>
       </c>
@@ -3530,7 +3534,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
     </row>
-    <row r="43" spans="1:20" ht="42">
+    <row r="43" spans="1:20" ht="40.5">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -3592,7 +3596,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -3602,7 +3606,7 @@
     <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.5">
+    <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="13" t="s">
         <v>176</v>
       </c>
@@ -3648,7 +3652,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28">
+    <row r="5" spans="1:6" ht="27">
       <c r="A5" s="6" t="s">
         <v>183</v>
       </c>
@@ -3667,7 +3671,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28">
+    <row r="6" spans="1:6" ht="27">
       <c r="A6" s="6" t="s">
         <v>186</v>
       </c>
@@ -3686,13 +3690,13 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28">
+    <row r="7" spans="1:6" ht="27">
       <c r="A7" s="6" t="s">
         <v>190</v>
       </c>
       <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -3705,13 +3709,13 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28">
+    <row r="8" spans="1:6" ht="27">
       <c r="A8" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B8" s="8">
         <f ca="1">COUNTIFS('Master Schedule'!P2:P43,"&lt;="&amp;TODAY(),'Master Schedule'!P2:P43,"&gt;0",'Master Schedule'!Q2:Q43,"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
@@ -3724,7 +3728,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28">
+    <row r="9" spans="1:6" ht="27">
       <c r="A9" s="6" t="s">
         <v>196</v>
       </c>
@@ -3769,7 +3773,7 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:6" ht="28">
+    <row r="13" spans="1:6" ht="27">
       <c r="A13" s="6" t="s">
         <v>200</v>
       </c>
@@ -3783,7 +3787,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="28">
+    <row r="14" spans="1:6" ht="27">
       <c r="A14" s="6" t="s">
         <v>203</v>
       </c>
@@ -3811,7 +3815,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="42">
+    <row r="16" spans="1:6" ht="40.5">
       <c r="A16" s="6" t="s">
         <v>209</v>
       </c>
@@ -3839,7 +3843,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="28">
+    <row r="18" spans="1:6" ht="27">
       <c r="A18" s="6" t="s">
         <v>215</v>
       </c>
@@ -3871,7 +3875,7 @@
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6" ht="42">
+    <row r="21" spans="1:6" ht="40.5">
       <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
@@ -3885,7 +3889,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="42">
+    <row r="22" spans="1:6" ht="40.5">
       <c r="A22" s="6" t="s">
         <v>121</v>
       </c>
@@ -3899,7 +3903,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="28">
+    <row r="23" spans="1:6" ht="27">
       <c r="A23" s="6" t="s">
         <v>155</v>
       </c>
@@ -3928,7 +3932,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3936,7 +3940,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28">
+    <row r="1" spans="1:4" ht="27">
       <c r="A1" s="1" t="s">
         <v>225</v>
       </c>
@@ -3950,7 +3954,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="42">
+    <row r="2" spans="1:4" ht="40.5">
       <c r="A2" s="2" t="s">
         <v>229</v>
       </c>
@@ -3964,7 +3968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28">
+    <row r="3" spans="1:4" ht="27">
       <c r="A3" s="4" t="s">
         <v>232</v>
       </c>
@@ -3978,7 +3982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28">
+    <row r="4" spans="1:4" ht="27">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -3992,7 +3996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28">
+    <row r="5" spans="1:4" ht="27">
       <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
@@ -4024,7 +4028,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="28">
+    <row r="8" spans="1:4" ht="27">
       <c r="A8" s="2" t="s">
         <v>241</v>
       </c>
@@ -4036,7 +4040,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="42">
+    <row r="9" spans="1:4" ht="40.5">
       <c r="A9" s="4" t="s">
         <v>244</v>
       </c>
@@ -4048,7 +4052,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="42">
+    <row r="10" spans="1:4" ht="40.5">
       <c r="A10" s="2" t="s">
         <v>247</v>
       </c>
@@ -4060,7 +4064,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" ht="42">
+    <row r="11" spans="1:4" ht="40.5">
       <c r="A11" s="4" t="s">
         <v>250</v>
       </c>
@@ -4072,7 +4076,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="42">
+    <row r="12" spans="1:4" ht="40.5">
       <c r="A12" s="2" t="s">
         <v>253</v>
       </c>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="28">
+    <row r="13" spans="1:4" ht="27">
       <c r="A13" s="4" t="s">
         <v>256</v>
       </c>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="42">
+    <row r="14" spans="1:4" ht="40.5">
       <c r="A14" s="2" t="s">
         <v>259</v>
       </c>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="42">
+    <row r="15" spans="1:4" ht="40.5">
       <c r="A15" s="4" t="s">
         <v>262</v>
       </c>
@@ -4120,7 +4124,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="42">
+    <row r="16" spans="1:4" ht="40.5">
       <c r="A16" s="2" t="s">
         <v>265</v>
       </c>
@@ -4132,7 +4136,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="42">
+    <row r="17" spans="1:4" ht="40.5">
       <c r="A17" s="4" t="s">
         <v>268</v>
       </c>
@@ -4153,7 +4157,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4166,7 +4170,7 @@
     <col min="9" max="9" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.5">
+    <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="16" t="s">
         <v>271</v>
       </c>
@@ -4192,7 +4196,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" ht="28">
+    <row r="3" spans="1:9" ht="27">
       <c r="A3" s="1" t="s">
         <v>273</v>
       </c>
@@ -4221,7 +4225,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="28">
+    <row r="4" spans="1:9" ht="27">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -4250,7 +4254,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28">
+    <row r="5" spans="1:9" ht="27">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -4279,7 +4283,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="42">
+    <row r="6" spans="1:9" ht="40.5">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -4308,7 +4312,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="42">
+    <row r="7" spans="1:9" ht="40.5">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -4337,7 +4341,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="28">
+    <row r="8" spans="1:9" ht="27">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -4366,7 +4370,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="28">
+    <row r="9" spans="1:9" ht="27">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -4482,7 +4486,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="28">
+    <row r="13" spans="1:9" ht="27">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -4540,7 +4544,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28">
+    <row r="15" spans="1:9" ht="27">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -4569,7 +4573,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="42">
+    <row r="16" spans="1:9" ht="40.5">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -4598,7 +4602,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28">
+    <row r="17" spans="1:9" ht="27">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -4627,7 +4631,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="28">
+    <row r="18" spans="1:9" ht="27">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -4656,7 +4660,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="28">
+    <row r="19" spans="1:9" ht="27">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -4685,7 +4689,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28">
+    <row r="20" spans="1:9" ht="27">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -4772,7 +4776,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="28">
+    <row r="23" spans="1:9" ht="27">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -4801,7 +4805,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="28">
+    <row r="24" spans="1:9" ht="27">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -4859,7 +4863,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="28">
+    <row r="26" spans="1:9" ht="27">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -4888,7 +4892,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="28">
+    <row r="27" spans="1:9" ht="27">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -4917,7 +4921,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="28">
+    <row r="28" spans="1:9" ht="27">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -5004,7 +5008,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="28">
+    <row r="31" spans="1:9" ht="27">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -5062,7 +5066,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="28">
+    <row r="33" spans="1:9" ht="27">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -5091,7 +5095,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="28">
+    <row r="34" spans="1:9" ht="27">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -5149,7 +5153,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="28">
+    <row r="36" spans="1:9" ht="27">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -5207,7 +5211,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="28">
+    <row r="38" spans="1:9" ht="27">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -5236,7 +5240,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="28">
+    <row r="39" spans="1:9" ht="27">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -5278,7 +5282,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5292,7 +5296,7 @@
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.5">
+    <row r="1" spans="1:11" ht="18.75">
       <c r="A1" s="16" t="s">
         <v>404</v>
       </c>
@@ -5322,7 +5326,7 @@
       <c r="J2" s="17"/>
       <c r="K2" s="17"/>
     </row>
-    <row r="3" spans="1:11" ht="28">
+    <row r="3" spans="1:11" ht="27">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="70">
+    <row r="4" spans="1:11" ht="67.5">
       <c r="A4" s="2" t="s">
         <v>415</v>
       </c>
@@ -5386,7 +5390,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="56">
+    <row r="5" spans="1:11" ht="54">
       <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
@@ -5413,7 +5417,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="56">
+    <row r="6" spans="1:11" ht="54">
       <c r="A6" s="2" t="s">
         <v>429</v>
       </c>
@@ -5438,7 +5442,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="42">
+    <row r="7" spans="1:11" ht="40.5">
       <c r="A7" s="4" t="s">
         <v>435</v>
       </c>
@@ -5461,7 +5465,7 @@
       <c r="J7" s="5"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="42">
+    <row r="8" spans="1:11" ht="40.5">
       <c r="A8" s="2" t="s">
         <v>439</v>
       </c>
@@ -5488,7 +5492,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="56">
+    <row r="9" spans="1:11" ht="54">
       <c r="A9" s="4" t="s">
         <v>98</v>
       </c>
@@ -5515,7 +5519,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="56">
+    <row r="10" spans="1:11" ht="54">
       <c r="A10" s="2" t="s">
         <v>452</v>
       </c>
@@ -5538,7 +5542,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="42">
+    <row r="11" spans="1:11" ht="40.5">
       <c r="A11" s="4" t="s">
         <v>457</v>
       </c>
@@ -5565,7 +5569,7 @@
       <c r="J11" s="5"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="42">
+    <row r="12" spans="1:11" ht="40.5">
       <c r="A12" s="2" t="s">
         <v>463</v>
       </c>
@@ -5590,7 +5594,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="42">
+    <row r="13" spans="1:11" ht="40.5">
       <c r="A13" s="4" t="s">
         <v>142</v>
       </c>
@@ -5615,7 +5619,7 @@
       <c r="J13" s="5"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="42">
+    <row r="14" spans="1:11" ht="40.5">
       <c r="A14" s="2" t="s">
         <v>474</v>
       </c>

--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_DE2EFB3A9D1E79C6859C80A3377C0E0772D29E3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF23E7C9-3F0B-47DB-9547-EF99EC340627}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_DE2EFB3A9D1E79C6859C80A3377C0E0772D29E3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB6DB31-E324-4919-B6CC-63C6CE377F82}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -1642,6 +1642,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2741,13 +2745,17 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="6"/>
+      <c r="L21" s="12">
+        <v>46300</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>232</v>
+      </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
-      <c r="P21" s="12" t="str">
+      <c r="P21" s="12">
         <f>IF(AND($L21&lt;&gt;"",$M21&lt;&gt;""),$L21+VLOOKUP($M21,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46302</v>
       </c>
       <c r="Q21" s="12"/>
       <c r="R21" s="6"/>
@@ -3696,7 +3704,7 @@
       </c>
       <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -3715,7 +3723,7 @@
       </c>
       <c r="B8" s="8">
         <f ca="1">COUNTIFS('Master Schedule'!P2:P43,"&lt;="&amp;TODAY(),'Master Schedule'!P2:P43,"&gt;0",'Master Schedule'!Q2:Q43,"")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">

--- a/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
+++ b/plan/Chapter8_Final_Section_Exercise_Redo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_DE2EFB3A9D1E79C6859C80A3377C0E0772D29E3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB6DB31-E324-4919-B6CC-63C6CE377F82}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_4A10487BE2825A7980104F5CE81F24FBE394D2B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEDB3B7-0C68-4F70-AC99-D7963A926EE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2385" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="481">
   <si>
     <t>Order</t>
   </si>
@@ -330,6 +330,9 @@
     <t>Strengthen pointwise/weak cdf convergence to uniform convergence when the limit is continuous.</t>
   </si>
   <si>
+    <t>Spark</t>
+  </si>
+  <si>
     <t>Ex 9</t>
   </si>
   <si>
@@ -733,9 +736,6 @@
   </si>
   <si>
     <t>Repair the exercise first. Redo next day after rereading the exact theorem/definition; ask for a minimum hint only if still blank.</t>
-  </si>
-  <si>
-    <t>Spark</t>
   </si>
   <si>
     <t>A blurred idea appears but cannot yet carry the proof.</t>
@@ -1642,10 +1642,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2749,7 +2745,7 @@
         <v>46300</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>232</v>
+        <v>97</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
@@ -2775,26 +2771,30 @@
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="10"/>
+      <c r="L22" s="11">
+        <v>46301</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
-      <c r="P22" s="11" t="str">
+      <c r="P22" s="11">
         <f>IF(AND($L22&lt;&gt;"",$M22&lt;&gt;""),$L22+VLOOKUP($M22,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46303</v>
       </c>
       <c r="Q22" s="11"/>
       <c r="R22" s="10"/>
@@ -2814,26 +2814,30 @@
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="6"/>
+      <c r="L23" s="12">
+        <v>46303</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
-      <c r="P23" s="12" t="str">
+      <c r="P23" s="12">
         <f>IF(AND($L23&lt;&gt;"",$M23&lt;&gt;""),$L23+VLOOKUP($M23,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46305</v>
       </c>
       <c r="Q23" s="12"/>
       <c r="R23" s="6"/>
@@ -2848,21 +2852,23 @@
         <v>46295</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
+      <c r="J24" s="11">
+        <v>46307</v>
+      </c>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
       <c r="M24" s="10"/>
@@ -2882,31 +2888,35 @@
         <v>46296</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="6"/>
+      <c r="L25" s="12">
+        <v>46308</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
-      <c r="P25" s="12" t="str">
+      <c r="P25" s="12">
         <f>IF(AND($L25&lt;&gt;"",$M25&lt;&gt;""),$L25+VLOOKUP($M25,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46310</v>
       </c>
       <c r="Q25" s="12"/>
       <c r="R25" s="6"/>
@@ -2921,31 +2931,35 @@
         <v>46297</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>94</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="10"/>
+      <c r="L26" s="11">
+        <v>46309</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
-      <c r="P26" s="11" t="str">
+      <c r="P26" s="11">
         <f>IF(AND($L26&lt;&gt;"",$M26&lt;&gt;""),$L26+VLOOKUP($M26,'Redo Rules'!$A$2:$D$5,4,FALSE),"")</f>
-        <v/>
+        <v>46311</v>
       </c>
       <c r="Q26" s="11"/>
       <c r="R26" s="10"/>
@@ -2960,18 +2974,18 @@
         <v>46298</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="12"/>
@@ -2994,21 +3008,21 @@
         <v>46299</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>46</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -3033,21 +3047,21 @@
         <v>46300</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
@@ -3072,21 +3086,21 @@
         <v>46301</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -3108,19 +3122,19 @@
         <v>46302</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
@@ -3142,21 +3156,21 @@
         <v>46303</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -3178,21 +3192,21 @@
         <v>46304</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J33" s="12"/>
       <c r="K33" s="12"/>
@@ -3217,21 +3231,21 @@
         <v>46305</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -3256,18 +3270,18 @@
         <v>46306</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="12"/>
@@ -3290,21 +3304,21 @@
         <v>46307</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -3329,21 +3343,21 @@
         <v>46308</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>33</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J37" s="12"/>
       <c r="K37" s="12"/>
@@ -3368,21 +3382,21 @@
         <v>46309</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -3407,21 +3421,21 @@
         <v>46310</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
@@ -3446,19 +3460,19 @@
         <v>46311</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
       <c r="H40" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -3480,21 +3494,21 @@
         <v>46312</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J41" s="12"/>
       <c r="K41" s="12"/>
@@ -3516,19 +3530,19 @@
         <v>46313</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
       <c r="H42" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -3550,19 +3564,19 @@
         <v>46314</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
@@ -3584,14 +3598,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="M2:M43" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="R2:R43" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Independent,Still Spark,Still Skeleton,Needs Hint,Parked"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="M2:M43" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Totally ignorance,Spark,Skeleton,Crack it"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:O43" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="O2:O43" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Yes,No,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="R2:R43" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"Independent,Still Spark,Still Skeleton,Needs Hint,Parked"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S43" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Yes,No,Not requested"</formula1>
@@ -3616,7 +3630,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3626,7 +3640,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -3644,25 +3658,25 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27">
       <c r="A5" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="8">
         <f>COUNTIF('Exercise Map'!F4:F39,"Yes")</f>
@@ -3673,15 +3687,15 @@
         <v>43</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27">
       <c r="A6" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF('Exercise Map'!F4:F39,"No")</f>
@@ -3689,56 +3703,56 @@
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27">
       <c r="A7" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B7" s="8">
         <f>COUNT('Master Schedule'!L2:L43)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27">
       <c r="A8" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B8" s="8">
         <f ca="1">COUNTIFS('Master Schedule'!P2:P43,"&lt;="&amp;TODAY(),'Master Schedule'!P2:P43,"&gt;0",'Master Schedule'!Q2:Q43,"")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27">
       <c r="A9" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B9" s="8">
         <f>COUNT('Section Plan'!J4:J14)</f>
@@ -3746,13 +3760,13 @@
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3773,7 +3787,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -3783,13 +3797,13 @@
     </row>
     <row r="13" spans="1:6" ht="27">
       <c r="A13" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -3797,13 +3811,13 @@
     </row>
     <row r="14" spans="1:6" ht="27">
       <c r="A14" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -3811,13 +3825,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -3825,13 +3839,13 @@
     </row>
     <row r="16" spans="1:6" ht="40.5">
       <c r="A16" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -3839,13 +3853,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -3853,13 +3867,13 @@
     </row>
     <row r="18" spans="1:6" ht="27">
       <c r="A18" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -3875,7 +3889,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -3888,10 +3902,10 @@
         <v>32</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -3899,13 +3913,13 @@
     </row>
     <row r="22" spans="1:6" ht="40.5">
       <c r="A22" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -3913,13 +3927,13 @@
     </row>
     <row r="23" spans="1:6" ht="27">
       <c r="A23" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -3950,27 +3964,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="40.5">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3978,7 +3992,7 @@
     </row>
     <row r="3" spans="1:4" ht="27">
       <c r="A3" s="4" t="s">
-        <v>232</v>
+        <v>97</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>233</v>
@@ -4029,7 +4043,7 @@
         <v>239</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>240</v>
@@ -4644,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>321</v>
@@ -4673,7 +4687,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>340</v>
@@ -4963,7 +4977,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>371</v>
@@ -4992,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>340</v>
@@ -5050,7 +5064,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>321</v>
@@ -5502,7 +5516,7 @@
     </row>
     <row r="9" spans="1:11" ht="54">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>446</v>
@@ -5561,7 +5575,7 @@
         <v>459</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>460</v>
@@ -5604,7 +5618,7 @@
     </row>
     <row r="13" spans="1:11" ht="40.5">
       <c r="A13" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>469</v>
